--- a/Fact_Global_Master.xlsx
+++ b/Fact_Global_Master.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID_Futmondo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Jornada</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Temporada</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Puntos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Puntos_Acumulados</t>
         </is>

--- a/Fact_Global_Master.xlsx
+++ b/Fact_Global_Master.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,47 +429,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID_Futmondo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Jornada</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Temporada</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Puntos</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Puntos_Acumulados</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acumulado_Total</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ranking_Jornada</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ranking_Temporada</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ranking_General</t>
         </is>
@@ -48514,7 +48526,7 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B1458" t="n">
@@ -48526,28 +48538,28 @@
         </is>
       </c>
       <c r="D1458" t="n">
-        <v>87.09999999999999</v>
+        <v>100.6</v>
       </c>
       <c r="E1458" t="n">
-        <v>2176</v>
+        <v>2212.7</v>
       </c>
       <c r="F1458" t="n">
-        <v>9711</v>
+        <v>12923.8</v>
       </c>
       <c r="G1458" t="n">
         <v>1</v>
       </c>
       <c r="H1458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1458" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B1459" t="n">
@@ -48559,22 +48571,22 @@
         </is>
       </c>
       <c r="D1459" t="n">
-        <v>81.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="E1459" t="n">
-        <v>2193.5</v>
+        <v>2176.9</v>
       </c>
       <c r="F1459" t="n">
-        <v>12904.6</v>
+        <v>9711.9</v>
       </c>
       <c r="G1459" t="n">
         <v>2</v>
       </c>
       <c r="H1459" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1459" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1460">
@@ -48592,13 +48604,13 @@
         </is>
       </c>
       <c r="D1460" t="n">
-        <v>59.5</v>
+        <v>73.7</v>
       </c>
       <c r="E1460" t="n">
-        <v>1746</v>
+        <v>1760.2</v>
       </c>
       <c r="F1460" t="n">
-        <v>10579.9</v>
+        <v>10594.1</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -48613,7 +48625,7 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B1461" t="n">
@@ -48625,28 +48637,28 @@
         </is>
       </c>
       <c r="D1461" t="n">
-        <v>52.9</v>
+        <v>70.8</v>
       </c>
       <c r="E1461" t="n">
-        <v>2004</v>
+        <v>2082.1</v>
       </c>
       <c r="F1461" t="n">
-        <v>11608.1</v>
+        <v>11947.2</v>
       </c>
       <c r="G1461" t="n">
         <v>4</v>
       </c>
       <c r="H1461" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1461" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B1462" t="n">
@@ -48658,22 +48670,22 @@
         </is>
       </c>
       <c r="D1462" t="n">
-        <v>48.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E1462" t="n">
-        <v>2059.6</v>
+        <v>2136.1</v>
       </c>
       <c r="F1462" t="n">
-        <v>11924.7</v>
+        <v>12827.1</v>
       </c>
       <c r="G1462" t="n">
         <v>5</v>
       </c>
       <c r="H1462" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1462" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1463">
@@ -48691,19 +48703,19 @@
         </is>
       </c>
       <c r="D1463" t="n">
-        <v>39.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E1463" t="n">
-        <v>2189.7</v>
+        <v>2214.6</v>
       </c>
       <c r="F1463" t="n">
-        <v>13124.5</v>
+        <v>13149.4</v>
       </c>
       <c r="G1463" t="n">
         <v>6</v>
       </c>
       <c r="H1463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1463" t="n">
         <v>1</v>
@@ -48724,13 +48736,13 @@
         </is>
       </c>
       <c r="D1464" t="n">
-        <v>28.1</v>
+        <v>60.5</v>
       </c>
       <c r="E1464" t="n">
-        <v>1862.3</v>
+        <v>1894.7</v>
       </c>
       <c r="F1464" t="n">
-        <v>11526.9</v>
+        <v>11559.3</v>
       </c>
       <c r="G1464" t="n">
         <v>7</v>
@@ -48745,7 +48757,7 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B1465" t="n">
@@ -48757,22 +48769,22 @@
         </is>
       </c>
       <c r="D1465" t="n">
-        <v>24.8</v>
+        <v>55.2</v>
       </c>
       <c r="E1465" t="n">
-        <v>2095</v>
+        <v>2006.3</v>
       </c>
       <c r="F1465" t="n">
-        <v>12786</v>
+        <v>11610.4</v>
       </c>
       <c r="G1465" t="n">
         <v>8</v>
       </c>
       <c r="H1465" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1465" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Fact_Global_Master.xlsx
+++ b/Fact_Global_Master.xlsx
@@ -48514,7 +48514,7 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>62d5bd9ad8106d3355b5bdc1</t>
+          <t>5f452f5e66dd374930eb2b71</t>
         </is>
       </c>
       <c r="B1458" t="n">
@@ -48526,28 +48526,28 @@
         </is>
       </c>
       <c r="D1458" t="n">
-        <v>87.09999999999999</v>
+        <v>100.6</v>
       </c>
       <c r="E1458" t="n">
-        <v>2176</v>
+        <v>2212.7</v>
       </c>
       <c r="F1458" t="n">
-        <v>9711</v>
+        <v>12923.8</v>
       </c>
       <c r="G1458" t="n">
         <v>1</v>
       </c>
       <c r="H1458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1458" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>5f452f5e66dd374930eb2b71</t>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
         </is>
       </c>
       <c r="B1459" t="n">
@@ -48559,22 +48559,22 @@
         </is>
       </c>
       <c r="D1459" t="n">
-        <v>81.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="E1459" t="n">
-        <v>2193.5</v>
+        <v>2176.9</v>
       </c>
       <c r="F1459" t="n">
-        <v>12904.6</v>
+        <v>9711.9</v>
       </c>
       <c r="G1459" t="n">
         <v>2</v>
       </c>
       <c r="H1459" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1459" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1460">
@@ -48592,13 +48592,13 @@
         </is>
       </c>
       <c r="D1460" t="n">
-        <v>59.5</v>
+        <v>73.7</v>
       </c>
       <c r="E1460" t="n">
-        <v>1746</v>
+        <v>1760.2</v>
       </c>
       <c r="F1460" t="n">
-        <v>10579.9</v>
+        <v>10594.1</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -48613,7 +48613,7 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>5f47aeb6c387a50bca03dd55</t>
+          <t>5f4530beec331549297ee6d6</t>
         </is>
       </c>
       <c r="B1461" t="n">
@@ -48625,28 +48625,28 @@
         </is>
       </c>
       <c r="D1461" t="n">
-        <v>52.9</v>
+        <v>70.8</v>
       </c>
       <c r="E1461" t="n">
-        <v>2004</v>
+        <v>2082.1</v>
       </c>
       <c r="F1461" t="n">
-        <v>11608.1</v>
+        <v>11947.2</v>
       </c>
       <c r="G1461" t="n">
         <v>4</v>
       </c>
       <c r="H1461" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1461" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>5f4530beec331549297ee6d6</t>
+          <t>5f453062ec331549297ee6b8</t>
         </is>
       </c>
       <c r="B1462" t="n">
@@ -48658,22 +48658,22 @@
         </is>
       </c>
       <c r="D1462" t="n">
-        <v>48.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E1462" t="n">
-        <v>2059.6</v>
+        <v>2136.1</v>
       </c>
       <c r="F1462" t="n">
-        <v>11924.7</v>
+        <v>12827.1</v>
       </c>
       <c r="G1462" t="n">
         <v>5</v>
       </c>
       <c r="H1462" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1462" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1463">
@@ -48691,19 +48691,19 @@
         </is>
       </c>
       <c r="D1463" t="n">
-        <v>39.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E1463" t="n">
-        <v>2189.7</v>
+        <v>2214.6</v>
       </c>
       <c r="F1463" t="n">
-        <v>13124.5</v>
+        <v>13149.4</v>
       </c>
       <c r="G1463" t="n">
         <v>6</v>
       </c>
       <c r="H1463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1463" t="n">
         <v>1</v>
@@ -48724,13 +48724,13 @@
         </is>
       </c>
       <c r="D1464" t="n">
-        <v>28.1</v>
+        <v>60.5</v>
       </c>
       <c r="E1464" t="n">
-        <v>1862.3</v>
+        <v>1894.7</v>
       </c>
       <c r="F1464" t="n">
-        <v>11526.9</v>
+        <v>11559.3</v>
       </c>
       <c r="G1464" t="n">
         <v>7</v>
@@ -48745,7 +48745,7 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>5f453062ec331549297ee6b8</t>
+          <t>5f47aeb6c387a50bca03dd55</t>
         </is>
       </c>
       <c r="B1465" t="n">
@@ -48757,22 +48757,22 @@
         </is>
       </c>
       <c r="D1465" t="n">
-        <v>24.8</v>
+        <v>55.2</v>
       </c>
       <c r="E1465" t="n">
-        <v>2095</v>
+        <v>2006.3</v>
       </c>
       <c r="F1465" t="n">
-        <v>12786</v>
+        <v>11610.4</v>
       </c>
       <c r="G1465" t="n">
         <v>8</v>
       </c>
       <c r="H1465" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1465" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
